--- a/outputs/monitor_xlsx/20260320.xlsx
+++ b/outputs/monitor_xlsx/20260320.xlsx
@@ -544,10 +544,6 @@
           <t>-0.43%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-0.42%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+2.55%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-0.66%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.72%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>-2.45%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+11.31%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+2.27%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>-403.11億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-331.18億</t>
@@ -811,7 +774,6 @@
           <t>10.58億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>1.91億</t>
@@ -822,8 +784,6 @@
           <t>9.54億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>145.58%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>139.76%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-493.58億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>10462口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>13362口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>31.12億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-30.15億</t>
@@ -1020,10 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1180,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2431,6 +2374,112 @@
       <c r="W22" t="inlineStr">
         <is>
           <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>6515</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>穎崴</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>7930</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="E23" t="n">
+        <v>443</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="G23" t="n">
+        <v>250</v>
+      </c>
+      <c r="H23" t="n">
+        <v>25</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J23" t="n">
+        <v>13</v>
+      </c>
+      <c r="K23" t="n">
+        <v>249</v>
+      </c>
+      <c r="L23" t="n">
+        <v>1268</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-8976</v>
+      </c>
+      <c r="N23" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>中性</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>致茂</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1585</v>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5103</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>-312</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-2075</v>
+      </c>
+      <c r="H24" t="n">
+        <v>288</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1226</v>
+      </c>
+      <c r="J24" t="n">
+        <v>103</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3239</v>
+      </c>
+      <c r="L24" t="n">
+        <v>13262</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-106290</v>
+      </c>
+      <c r="N24" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260320.xlsx
+++ b/outputs/monitor_xlsx/20260320.xlsx
@@ -544,6 +544,10 @@
           <t>-0.43%</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -566,6 +570,10 @@
           <t>-0.42%</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -588,6 +596,10 @@
           <t>+0.00%</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -610,6 +622,10 @@
           <t>+2.55%</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -632,6 +648,10 @@
           <t>-0.66%</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -654,6 +674,10 @@
           <t>-0.72%</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -676,6 +700,10 @@
           <t>-2.45%</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -698,6 +726,10 @@
           <t>+11.31%</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -720,6 +752,10 @@
           <t>+2.27%</t>
         </is>
       </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -737,6 +773,7 @@
           <t>-403.11億</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-331.18億</t>
@@ -774,6 +811,7 @@
           <t>10.58億</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>1.91億</t>
@@ -784,6 +822,8 @@
           <t>9.54億</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -798,14 +838,18 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>145.58%</t>
-        </is>
-      </c>
+          <t>141.14%</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>139.76%</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -823,6 +867,11 @@
           <t>-493.58億</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -840,11 +889,15 @@
           <t>10462口</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>13362口</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -862,6 +915,7 @@
           <t>31.12億</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-30.15億</t>
@@ -874,12 +928,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-18.99億</t>
+          <t>None億</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-379.89億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -966,6 +1020,10 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
+    </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1029,7 +1087,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>-18.99億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1099,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>-379.89億</t>
+          <t>None億</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1145,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W24"/>
+  <dimension ref="A1:V16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1105,14 +1163,13 @@
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
     <col width="14" customWidth="1" min="18" max="18"/>
-    <col width="14" customWidth="1" min="19" max="19"/>
-    <col width="12" customWidth="1" min="20" max="20"/>
-    <col width="10" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="12" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="10" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1122,7 +1179,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -1201,40 +1257,35 @@
       </c>
       <c r="P3" s="5" t="inlineStr">
         <is>
-          <t>籌碼評價</t>
+          <t>買賣券商差</t>
         </is>
       </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
-          <t>買賣券商差</t>
+          <t>籌碼集中度5D(%)</t>
         </is>
       </c>
       <c r="R3" s="5" t="inlineStr">
         <is>
-          <t>籌碼集中度5D(%)</t>
+          <t>借券賣出餘額</t>
         </is>
       </c>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>借券賣出餘額</t>
+          <t>短回補天數</t>
         </is>
       </c>
       <c r="T3" s="5" t="inlineStr">
         <is>
-          <t>短回補天數</t>
+          <t>VWAP20D</t>
         </is>
       </c>
       <c r="U3" s="5" t="inlineStr">
         <is>
-          <t>VWAP20D</t>
+          <t>VWAP乖離(%)</t>
         </is>
       </c>
       <c r="V3" s="5" t="inlineStr">
-        <is>
-          <t>VWAP乖離(%)</t>
-        </is>
-      </c>
-      <c r="W3" s="5" t="inlineStr">
         <is>
           <t>資料來源</t>
         </is>
@@ -1289,12 +1340,7 @@
       <c r="N4" t="n">
         <v>-4479831</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1349,12 +1395,7 @@
       <c r="N5" t="n">
         <v>-78835</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1409,12 +1450,7 @@
       <c r="N6" t="n">
         <v>-649378</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1469,12 +1505,7 @@
       <c r="N7" t="n">
         <v>-6483124</v>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1483,12 +1514,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>華邦電</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1497,44 +1528,39 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>110</v>
-      </c>
-      <c r="E8" s="6" t="n">
-        <v>-9.84</v>
+        <v>1610</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>1.26</v>
       </c>
       <c r="F8" t="n">
-        <v>338024</v>
+        <v>5787</v>
       </c>
       <c r="G8" s="7" t="n">
-        <v>-132952</v>
+        <v>-346</v>
       </c>
       <c r="H8" t="n">
-        <v>42371</v>
+        <v>727</v>
       </c>
       <c r="I8" t="n">
-        <v>67026</v>
+        <v>44</v>
       </c>
       <c r="J8" t="n">
-        <v>54</v>
+        <v>-70</v>
       </c>
       <c r="K8" t="n">
-        <v>8125</v>
+        <v>143</v>
       </c>
       <c r="L8" t="n">
-        <v>133650</v>
+        <v>2196</v>
       </c>
       <c r="M8" t="n">
-        <v>529217</v>
+        <v>8946</v>
       </c>
       <c r="N8" t="n">
-        <v>-1119491</v>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
+        <v>-140174</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1543,12 +1569,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2383</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>台光電</t>
+          <t>致茂</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1557,44 +1583,39 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2810</v>
+        <v>1585</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>-2.77</v>
+        <v>-0.63</v>
       </c>
       <c r="F9" t="n">
-        <v>4588</v>
+        <v>5103</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>-949</v>
+        <v>-312</v>
       </c>
       <c r="H9" t="n">
-        <v>-292</v>
+        <v>-1763</v>
       </c>
       <c r="I9" t="n">
-        <v>83</v>
+        <v>288</v>
       </c>
       <c r="J9" t="n">
-        <v>-76</v>
+        <v>939</v>
       </c>
       <c r="K9" t="n">
-        <v>164</v>
+        <v>103</v>
       </c>
       <c r="L9" t="n">
-        <v>1989</v>
+        <v>3239</v>
       </c>
       <c r="M9" t="n">
-        <v>7711</v>
+        <v>13487</v>
       </c>
       <c r="N9" t="n">
-        <v>-89575</v>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>-106290</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1603,12 +1624,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2383</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>台光電</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1617,44 +1638,39 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3375</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>4.81</v>
+        <v>2810</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>-2.77</v>
       </c>
       <c r="F10" t="n">
-        <v>4114</v>
-      </c>
-      <c r="G10" s="6" t="n">
-        <v>743</v>
+        <v>4588</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>-949</v>
       </c>
       <c r="H10" t="n">
-        <v>223</v>
+        <v>-292</v>
       </c>
       <c r="I10" t="n">
-        <v>-95</v>
+        <v>83</v>
       </c>
       <c r="J10" t="n">
-        <v>-353</v>
+        <v>-76</v>
       </c>
       <c r="K10" t="n">
-        <v>274</v>
+        <v>164</v>
       </c>
       <c r="L10" t="n">
-        <v>5821</v>
+        <v>1989</v>
       </c>
       <c r="M10" t="n">
-        <v>23134</v>
+        <v>7711</v>
       </c>
       <c r="N10" t="n">
-        <v>-19781</v>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
+        <v>-89575</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1709,12 +1725,7 @@
       <c r="N11" t="n">
         <v>-19480</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1723,58 +1734,53 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>6515</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>聯亞</t>
+          <t>穎崴</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1640</v>
+        <v>7930</v>
       </c>
       <c r="E12" s="7" t="n">
-        <v>6.49</v>
+        <v>9.99</v>
       </c>
       <c r="F12" t="n">
-        <v>1208</v>
+        <v>443</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>267</v>
+        <v>79</v>
       </c>
       <c r="H12" t="n">
-        <v>327</v>
+        <v>170</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J12" t="n">
-        <v>52</v>
+        <v>-29</v>
       </c>
       <c r="K12" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="L12" t="n">
-        <v>-106</v>
+        <v>249</v>
       </c>
       <c r="M12" t="n">
-        <v>-566</v>
+        <v>1019</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
+        <v>-8976</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1783,12 +1789,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>4979</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>華星光</t>
+          <t>聯亞</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1797,44 +1803,39 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>404.5</v>
+        <v>2315</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>3.32</v>
+        <v>9.98</v>
       </c>
       <c r="F13" t="n">
-        <v>27950</v>
+        <v>2730</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>737</v>
+        <v>267</v>
       </c>
       <c r="H13" t="n">
-        <v>-5363</v>
+        <v>327</v>
       </c>
       <c r="I13" t="n">
-        <v>771</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>-3835</v>
+        <v>52</v>
       </c>
       <c r="K13" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L13" t="n">
-        <v>739</v>
+        <v>-106</v>
       </c>
       <c r="M13" t="n">
-        <v>1468</v>
+        <v>-566</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1843,12 +1844,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>3491</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>華星光</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1857,44 +1858,39 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1450</v>
+        <v>449.5</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>3.57</v>
+        <v>4.78</v>
       </c>
       <c r="F14" t="n">
-        <v>296</v>
+        <v>3871</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>51</v>
+        <v>737</v>
       </c>
       <c r="H14" t="n">
-        <v>-39</v>
+        <v>-5363</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>771</v>
       </c>
       <c r="J14" t="n">
-        <v>25</v>
+        <v>-3835</v>
       </c>
       <c r="K14" t="n">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="L14" t="n">
-        <v>-7</v>
+        <v>739</v>
       </c>
       <c r="M14" t="n">
-        <v>-106</v>
+        <v>1468</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1903,58 +1899,53 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>萬潤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>上市</t>
+          <t>上櫃</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1610</v>
+        <v>974</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>1.26</v>
+        <v>9.93</v>
       </c>
       <c r="F15" t="n">
-        <v>5787</v>
-      </c>
-      <c r="G15" s="7" t="n">
-        <v>-346</v>
+        <v>1350</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>248</v>
       </c>
       <c r="H15" t="n">
-        <v>727</v>
+        <v>116</v>
       </c>
       <c r="I15" t="n">
-        <v>44</v>
+        <v>806</v>
       </c>
       <c r="J15" t="n">
-        <v>-70</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>143</v>
+        <v>-31</v>
       </c>
       <c r="L15" t="n">
-        <v>2196</v>
+        <v>902</v>
       </c>
       <c r="M15" t="n">
-        <v>8946</v>
+        <v>-118</v>
       </c>
       <c r="N15" t="n">
-        <v>-140174</v>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1963,12 +1954,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>波若威</t>
+          <t>均華</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1977,509 +1968,41 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>912</v>
-      </c>
-      <c r="E16" s="6" t="n">
-        <v>-0.65</v>
+        <v>1600</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>4.92</v>
       </c>
       <c r="F16" t="n">
-        <v>1071</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>38</v>
+        <v>904</v>
+      </c>
+      <c r="G16" s="7" t="n">
+        <v>-30</v>
       </c>
       <c r="H16" t="n">
-        <v>-2507</v>
+        <v>186</v>
       </c>
       <c r="I16" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
         <v>27</v>
       </c>
-      <c r="J16" t="n">
-        <v>1206</v>
-      </c>
-      <c r="K16" t="n">
-        <v>13</v>
-      </c>
       <c r="L16" t="n">
-        <v>-101</v>
+        <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>1167</v>
+        <v>258</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2404</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>漢唐</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>930</v>
-      </c>
-      <c r="E17" s="7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6586</v>
-      </c>
-      <c r="G17" s="7" t="n">
-        <v>-1076</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-5897</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-137</v>
-      </c>
-      <c r="J17" t="n">
-        <v>-1654</v>
-      </c>
-      <c r="K17" t="n">
-        <v>159</v>
-      </c>
-      <c r="L17" t="n">
-        <v>3012</v>
-      </c>
-      <c r="M17" t="n">
-        <v>10366</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-47634</v>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>6640</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>均豪</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1165</v>
-      </c>
-      <c r="E18" s="7" t="n">
-        <v>6.39</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1035</v>
-      </c>
-      <c r="G18" s="7" t="n">
-        <v>-30</v>
-      </c>
-      <c r="H18" t="n">
-        <v>186</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
-        <v>27</v>
-      </c>
-      <c r="L18" t="n">
-        <v>54</v>
-      </c>
-      <c r="M18" t="n">
-        <v>258</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>6187</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>萬潤</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>819</v>
-      </c>
-      <c r="E19" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F19" t="n">
-        <v>7278</v>
-      </c>
-      <c r="G19" s="6" t="n">
-        <v>248</v>
-      </c>
-      <c r="H19" t="n">
-        <v>116</v>
-      </c>
-      <c r="I19" t="n">
-        <v>806</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-31</v>
-      </c>
-      <c r="L19" t="n">
-        <v>902</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-118</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>主力積極買進</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>3030</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>德律</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>255.5</v>
-      </c>
-      <c r="E20" s="6" t="n">
-        <v>-3.04</v>
-      </c>
-      <c r="F20" t="n">
-        <v>5299</v>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>536</v>
-      </c>
-      <c r="H20" t="n">
-        <v>-2590</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="J20" t="n">
-        <v>10</v>
-      </c>
-      <c r="K20" t="n">
-        <v>249</v>
-      </c>
-      <c r="L20" t="n">
-        <v>6708</v>
-      </c>
-      <c r="M20" t="n">
-        <v>28267</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-59054</v>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>偏空</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>1305</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>華夏</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="E21" s="7" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="F21" t="n">
-        <v>45892</v>
-      </c>
-      <c r="G21" s="7" t="n">
-        <v>-346</v>
-      </c>
-      <c r="H21" t="n">
-        <v>946</v>
-      </c>
-      <c r="I21" t="n">
-        <v>200</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K21" t="n">
-        <v>264</v>
-      </c>
-      <c r="L21" t="n">
-        <v>7688</v>
-      </c>
-      <c r="M21" t="n">
-        <v>28450</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-145259</v>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>偏多</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>1309</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>台達化</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>18.1</v>
-      </c>
-      <c r="E22" s="7" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="F22" t="n">
-        <v>46510</v>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>1792</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-74</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>645</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7634</v>
-      </c>
-      <c r="M22" t="n">
-        <v>32062</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-99395</v>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>主力積極賣出</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>6515</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>穎崴</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>7930</v>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>9.99</v>
-      </c>
-      <c r="E23" t="n">
-        <v>443</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>79</v>
-      </c>
-      <c r="G23" t="n">
-        <v>250</v>
-      </c>
-      <c r="H23" t="n">
-        <v>25</v>
-      </c>
-      <c r="I23" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J23" t="n">
-        <v>13</v>
-      </c>
-      <c r="K23" t="n">
-        <v>249</v>
-      </c>
-      <c r="L23" t="n">
-        <v>1268</v>
-      </c>
-      <c r="M23" t="n">
-        <v>-8976</v>
-      </c>
-      <c r="N23" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>中性</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>致茂</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>1585</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="E24" t="n">
-        <v>5103</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>-312</v>
-      </c>
-      <c r="G24" t="n">
-        <v>-2075</v>
-      </c>
-      <c r="H24" t="n">
-        <v>288</v>
-      </c>
-      <c r="I24" t="n">
-        <v>1226</v>
-      </c>
-      <c r="J24" t="n">
-        <v>103</v>
-      </c>
-      <c r="K24" t="n">
-        <v>3239</v>
-      </c>
-      <c r="L24" t="n">
-        <v>13262</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-106290</v>
-      </c>
-      <c r="N24" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>偏空</t>
         </is>
       </c>
     </row>

--- a/outputs/monitor_xlsx/20260320.xlsx
+++ b/outputs/monitor_xlsx/20260320.xlsx
@@ -544,10 +544,6 @@
           <t>-0.43%</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -570,10 +566,6 @@
           <t>-0.42%</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -596,10 +588,6 @@
           <t>+0.00%</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -622,10 +610,6 @@
           <t>+2.55%</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -648,10 +632,6 @@
           <t>-0.66%</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -674,10 +654,6 @@
           <t>-0.72%</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -700,10 +676,6 @@
           <t>-2.45%</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -726,10 +698,6 @@
           <t>+11.31%</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -752,10 +720,6 @@
           <t>+2.27%</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -773,7 +737,6 @@
           <t>-403.11億</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>-331.18億</t>
@@ -811,7 +774,6 @@
           <t>10.58億</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>1.91億</t>
@@ -822,8 +784,6 @@
           <t>9.54億</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -841,15 +801,11 @@
           <t>141.14%</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>139.76%</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -867,11 +823,6 @@
           <t>-493.58億</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -889,15 +840,11 @@
           <t>10462口</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>13362口</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -915,7 +862,6 @@
           <t>31.12億</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>-30.15億</t>
@@ -1020,10 +966,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1145,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V16"/>
+  <dimension ref="A1:V17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1179,6 +1122,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
@@ -2004,6 +1948,54 @@
         <is>
           <t>N/A</t>
         </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3167</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>大量</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>345</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-3.36</v>
+      </c>
+      <c r="E17" t="n">
+        <v>651</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>-170</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-1905</v>
+      </c>
+      <c r="H17" t="n">
+        <v>28</v>
+      </c>
+      <c r="I17" t="n">
+        <v>635</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8483</v>
+      </c>
+      <c r="L17" t="n">
+        <v>43966</v>
+      </c>
+      <c r="M17" t="n">
+        <v>-22109</v>
+      </c>
+      <c r="N17" t="n">
+        <v>11.53</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260320.xlsx
+++ b/outputs/monitor_xlsx/20260320.xlsx
@@ -966,7 +966,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
@@ -1243,7 +1242,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>元大台灣50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1251,26 +1250,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="6" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="E4" s="6" t="n">
         <v>-0.13</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="7" t="n">
         <v>72638</v>
       </c>
       <c r="G4" s="7" t="n">
         <v>-31151</v>
       </c>
       <c r="H4" t="n">
-        <v>-161517</v>
+        <v>-192668</v>
       </c>
       <c r="I4" t="n">
         <v>700</v>
       </c>
       <c r="J4" t="n">
-        <v>8614</v>
+        <v>9314</v>
       </c>
       <c r="K4" t="n">
         <v>12645</v>
@@ -1279,11 +1278,14 @@
         <v>13059</v>
       </c>
       <c r="M4" t="n">
-        <v>53145</v>
+        <v>66204</v>
       </c>
       <c r="N4" t="n">
         <v>-4479831</v>
       </c>
+      <c r="O4" t="n">
+        <v>-1.86</v>
+      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1306,26 +1308,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="6" t="n">
         <v>916</v>
       </c>
       <c r="E5" s="6" t="n">
         <v>-0.65</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="7" t="n">
         <v>2182</v>
       </c>
       <c r="G5" s="7" t="n">
         <v>-79</v>
       </c>
       <c r="H5" t="n">
-        <v>-322</v>
+        <v>-401</v>
       </c>
       <c r="I5" t="n">
         <v>6</v>
       </c>
       <c r="J5" t="n">
-        <v>-134</v>
+        <v>-128</v>
       </c>
       <c r="K5" t="n">
         <v>60</v>
@@ -1334,11 +1336,14 @@
         <v>2860</v>
       </c>
       <c r="M5" t="n">
-        <v>11500</v>
+        <v>14360</v>
       </c>
       <c r="N5" t="n">
         <v>-78835</v>
       </c>
+      <c r="O5" t="n">
+        <v>-3.4</v>
+      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1361,26 +1366,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="7" t="n">
         <v>1475</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>1.37</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="6" t="n">
         <v>15939</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>2239</v>
       </c>
       <c r="H6" t="n">
-        <v>5776</v>
+        <v>8015</v>
       </c>
       <c r="I6" t="n">
         <v>-420</v>
       </c>
       <c r="J6" t="n">
-        <v>-558</v>
+        <v>-979</v>
       </c>
       <c r="K6" t="n">
         <v>169</v>
@@ -1389,11 +1394,14 @@
         <v>5373</v>
       </c>
       <c r="M6" t="n">
-        <v>22283</v>
+        <v>27656</v>
       </c>
       <c r="N6" t="n">
         <v>-649378</v>
       </c>
+      <c r="O6" t="n">
+        <v>7.86</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1416,26 +1424,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="D7" s="6" t="n">
         <v>1840</v>
       </c>
       <c r="E7" s="6" t="n">
         <v>-0.54</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7" s="7" t="n">
         <v>53705</v>
       </c>
       <c r="G7" s="7" t="n">
         <v>-6769</v>
       </c>
       <c r="H7" t="n">
-        <v>-38821</v>
+        <v>-45590</v>
       </c>
       <c r="I7" t="n">
         <v>-4028</v>
       </c>
       <c r="J7" t="n">
-        <v>-1538</v>
+        <v>-5566</v>
       </c>
       <c r="K7" t="n">
         <v>624</v>
@@ -1444,11 +1452,14 @@
         <v>26115</v>
       </c>
       <c r="M7" t="n">
-        <v>102519</v>
+        <v>128634</v>
       </c>
       <c r="N7" t="n">
         <v>-6483124</v>
       </c>
+      <c r="O7" t="n">
+        <v>-3.2</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1471,26 +1482,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D8" s="7" t="n">
         <v>1610</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>1.26</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="7" t="n">
         <v>5787</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>-346</v>
       </c>
       <c r="H8" t="n">
-        <v>727</v>
+        <v>382</v>
       </c>
       <c r="I8" t="n">
         <v>44</v>
       </c>
       <c r="J8" t="n">
-        <v>-70</v>
+        <v>-27</v>
       </c>
       <c r="K8" t="n">
         <v>143</v>
@@ -1499,11 +1510,14 @@
         <v>2196</v>
       </c>
       <c r="M8" t="n">
-        <v>8946</v>
+        <v>11142</v>
       </c>
       <c r="N8" t="n">
         <v>-140174</v>
       </c>
+      <c r="O8" t="n">
+        <v>11.03</v>
+      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1526,26 +1540,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="D9" s="6" t="n">
         <v>1585</v>
       </c>
       <c r="E9" s="6" t="n">
         <v>-0.63</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F9" s="7" t="n">
         <v>5103</v>
       </c>
       <c r="G9" s="7" t="n">
         <v>-312</v>
       </c>
       <c r="H9" t="n">
-        <v>-1763</v>
+        <v>-2075</v>
       </c>
       <c r="I9" t="n">
         <v>288</v>
       </c>
       <c r="J9" t="n">
-        <v>939</v>
+        <v>1226</v>
       </c>
       <c r="K9" t="n">
         <v>103</v>
@@ -1554,11 +1568,14 @@
         <v>3239</v>
       </c>
       <c r="M9" t="n">
-        <v>13487</v>
+        <v>16726</v>
       </c>
       <c r="N9" t="n">
         <v>-106290</v>
       </c>
+      <c r="O9" t="n">
+        <v>13.7</v>
+      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1581,26 +1598,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D10" s="6" t="n">
         <v>2810</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>-2.77</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="7" t="n">
         <v>4588</v>
       </c>
       <c r="G10" s="7" t="n">
         <v>-949</v>
       </c>
       <c r="H10" t="n">
-        <v>-292</v>
+        <v>-1242</v>
       </c>
       <c r="I10" t="n">
         <v>83</v>
       </c>
       <c r="J10" t="n">
-        <v>-76</v>
+        <v>6</v>
       </c>
       <c r="K10" t="n">
         <v>164</v>
@@ -1609,11 +1626,14 @@
         <v>1989</v>
       </c>
       <c r="M10" t="n">
-        <v>7711</v>
+        <v>9700</v>
       </c>
       <c r="N10" t="n">
         <v>-89575</v>
       </c>
+      <c r="O10" t="n">
+        <v>14.36</v>
+      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1636,26 +1656,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="D11" s="7" t="n">
         <v>2045</v>
       </c>
       <c r="E11" s="7" t="n">
         <v>5.96</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="6" t="n">
         <v>804</v>
       </c>
       <c r="G11" s="6" t="n">
         <v>98</v>
       </c>
       <c r="H11" t="n">
-        <v>70</v>
+        <v>168</v>
       </c>
       <c r="I11" t="n">
         <v>81</v>
       </c>
       <c r="J11" t="n">
-        <v>-45</v>
+        <v>36</v>
       </c>
       <c r="K11" t="n">
         <v>25</v>
@@ -1664,11 +1684,14 @@
         <v>4054</v>
       </c>
       <c r="M11" t="n">
-        <v>16805</v>
+        <v>20859</v>
       </c>
       <c r="N11" t="n">
         <v>-19480</v>
       </c>
+      <c r="O11" t="n">
+        <v>5.53</v>
+      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1691,26 +1714,26 @@
           <t>上市</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="D12" s="7" t="n">
         <v>7930</v>
       </c>
       <c r="E12" s="7" t="n">
         <v>9.99</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="6" t="n">
         <v>443</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>79</v>
       </c>
       <c r="H12" t="n">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="I12" t="n">
         <v>25</v>
       </c>
       <c r="J12" t="n">
-        <v>-29</v>
+        <v>-4</v>
       </c>
       <c r="K12" t="n">
         <v>13</v>
@@ -1719,11 +1742,14 @@
         <v>249</v>
       </c>
       <c r="M12" t="n">
-        <v>1019</v>
+        <v>1268</v>
       </c>
       <c r="N12" t="n">
         <v>-8976</v>
       </c>
+      <c r="O12" t="n">
+        <v>40.67</v>
+      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1746,20 +1772,20 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>2315</v>
+      <c r="D13" s="7" t="n">
+        <v>2365</v>
       </c>
       <c r="E13" s="7" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="F13" t="n">
-        <v>2730</v>
+        <v>2.16</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>2182</v>
       </c>
       <c r="G13" s="6" t="n">
         <v>267</v>
       </c>
       <c r="H13" t="n">
-        <v>327</v>
+        <v>594</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1774,11 +1800,14 @@
         <v>-106</v>
       </c>
       <c r="M13" t="n">
-        <v>-566</v>
+        <v>-672</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
       </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="V13" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1801,26 +1830,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D14" t="n">
-        <v>449.5</v>
+      <c r="D14" s="7" t="n">
+        <v>586</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="F14" t="n">
-        <v>3871</v>
+        <v>9.94</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>32773</v>
       </c>
       <c r="G14" s="6" t="n">
         <v>737</v>
       </c>
       <c r="H14" t="n">
-        <v>-5363</v>
+        <v>-4626</v>
       </c>
       <c r="I14" t="n">
         <v>771</v>
       </c>
       <c r="J14" t="n">
-        <v>-3835</v>
+        <v>-3064</v>
       </c>
       <c r="K14" t="n">
         <v>53</v>
@@ -1829,11 +1858,14 @@
         <v>739</v>
       </c>
       <c r="M14" t="n">
-        <v>1468</v>
+        <v>2207</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
       </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="V14" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1856,26 +1888,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D15" t="n">
-        <v>974</v>
-      </c>
-      <c r="E15" s="7" t="n">
-        <v>9.93</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1350</v>
+      <c r="D15" s="6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>-2.64</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>6341</v>
       </c>
       <c r="G15" s="6" t="n">
         <v>248</v>
       </c>
       <c r="H15" t="n">
-        <v>116</v>
+        <v>364</v>
       </c>
       <c r="I15" t="n">
         <v>806</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>806</v>
       </c>
       <c r="K15" t="n">
         <v>-31</v>
@@ -1884,11 +1916,14 @@
         <v>902</v>
       </c>
       <c r="M15" t="n">
-        <v>-118</v>
+        <v>784</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="V15" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1911,26 +1946,26 @@
           <t>上櫃</t>
         </is>
       </c>
-      <c r="D16" t="n">
-        <v>1600</v>
-      </c>
-      <c r="E16" s="7" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="F16" t="n">
-        <v>904</v>
+      <c r="D16" s="6" t="n">
+        <v>1625</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-6.07</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>1168</v>
       </c>
       <c r="G16" s="7" t="n">
         <v>-30</v>
       </c>
       <c r="H16" t="n">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="I16" t="n">
         <v>-6</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="K16" t="n">
         <v>27</v>
@@ -1939,11 +1974,14 @@
         <v>54</v>
       </c>
       <c r="M16" t="n">
-        <v>258</v>
+        <v>312</v>
       </c>
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
       <c r="V16" t="inlineStr">
         <is>
           <t>N/A</t>
@@ -1961,41 +1999,46 @@
           <t>大量</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>345</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="E17" s="6" t="n">
         <v>-3.36</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" s="7" t="n">
         <v>651</v>
       </c>
-      <c r="F17" s="7" t="n">
+      <c r="G17" s="7" t="n">
         <v>-170</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>-1905</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>28</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>635</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>32</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>8483</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>43966</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>-22109</v>
       </c>
-      <c r="N17" t="n">
-        <v>11.53</v>
+      <c r="O17" t="n">
+        <v>10.31</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/monitor_xlsx/20260320.xlsx
+++ b/outputs/monitor_xlsx/20260320.xlsx
@@ -1087,7 +1087,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:V20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2041,165 @@
         <v>10.31</v>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>聯發科</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1700</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="F18" t="n">
+        <v>8267</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1100</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-4055</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-223</v>
+      </c>
+      <c r="J18" t="n">
+        <v>-975</v>
+      </c>
+      <c r="K18" t="n">
+        <v>133</v>
+      </c>
+      <c r="L18" t="n">
+        <v>6006</v>
+      </c>
+      <c r="M18" t="n">
+        <v>29998</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-400972</v>
+      </c>
+      <c r="O18" t="n">
+        <v>-2.54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>3037</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>欣興</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>554</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-4.65</v>
+      </c>
+      <c r="F19" t="n">
+        <v>9060</v>
+      </c>
+      <c r="G19" s="7" t="n">
+        <v>-122</v>
+      </c>
+      <c r="H19" t="n">
+        <v>10463</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-184</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1275</v>
+      </c>
+      <c r="K19" t="n">
+        <v>964</v>
+      </c>
+      <c r="L19" t="n">
+        <v>33849</v>
+      </c>
+      <c r="M19" t="n">
+        <v>175520</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-393016</v>
+      </c>
+      <c r="O19" t="n">
+        <v>13.57</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>8046</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>南電</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>541</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-3.57</v>
+      </c>
+      <c r="F20" t="n">
+        <v>20161</v>
+      </c>
+      <c r="G20" s="7" t="n">
+        <v>-157</v>
+      </c>
+      <c r="H20" t="n">
+        <v>-14108</v>
+      </c>
+      <c r="I20" t="n">
+        <v>181</v>
+      </c>
+      <c r="J20" t="n">
+        <v>6842</v>
+      </c>
+      <c r="K20" t="n">
+        <v>1256</v>
+      </c>
+      <c r="L20" t="n">
+        <v>10050</v>
+      </c>
+      <c r="M20" t="n">
+        <v>52931</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-161230</v>
+      </c>
+      <c r="O20" t="n">
+        <v>8.119999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:O1"/>
